--- a/output/pdf_financials_xlsx/AFE.xlsx
+++ b/output/pdf_financials_xlsx/AFE.xlsx
@@ -1807,50 +1807,32 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="3" t="n">
+        <v>-0.067493</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>-1.098</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>2.979</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>2.205</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>-92.348</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>-3.196</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>-4.198</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>-4.744</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>-13.085</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>21.564</v>
@@ -1858,10 +1840,8 @@
       <c r="L23" s="3" t="n">
         <v>-20.772</v>
       </c>
-      <c r="M23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M23" s="3" t="n">
+        <v>-119.776</v>
       </c>
     </row>
     <row r="24">
@@ -4080,7 +4060,7 @@
         <v>0</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="L70" s="3" t="n">
         <v>0</v>
@@ -4123,7 +4103,7 @@
         <v>0</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="L71" s="3" t="n">
         <v>0</v>
@@ -4295,7 +4275,7 @@
         <v>0</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="L75" s="3" t="n">
         <v>0</v>
@@ -4533,10 +4513,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K80" s="3" t="n">
+        <v>7.531169628299123e-06</v>
       </c>
       <c r="L80" s="1" t="inlineStr">
         <is>
@@ -5301,50 +5279,32 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-0.067493</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>-1.098</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>2.979</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>2.205</v>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>-92.348</v>
+      </c>
+      <c r="G99" s="3" t="n">
+        <v>-3.196</v>
+      </c>
+      <c r="H99" s="3" t="n">
+        <v>-4.198</v>
+      </c>
+      <c r="I99" s="3" t="n">
+        <v>-4.744</v>
+      </c>
+      <c r="J99" s="3" t="n">
+        <v>-13.085</v>
       </c>
       <c r="K99" s="3" t="n">
         <v>21.564</v>
@@ -5352,10 +5312,8 @@
       <c r="L99" s="3" t="n">
         <v>-20.772</v>
       </c>
-      <c r="M99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M99" s="3" t="n">
+        <v>-119.776</v>
       </c>
     </row>
     <row r="100">
@@ -5364,50 +5322,32 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K100" s="3" t="n">
         <v>0</v>
@@ -5415,10 +5355,8 @@
       <c r="L100" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -5427,50 +5365,32 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K101" s="3" t="n">
         <v>0</v>
@@ -5478,10 +5398,8 @@
       <c r="L101" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M101" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -5490,50 +5408,32 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K102" s="3" t="n">
         <v>0</v>
@@ -5541,10 +5441,8 @@
       <c r="L102" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -5553,50 +5451,32 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K103" s="3" t="n">
         <v>0</v>
@@ -5604,10 +5484,8 @@
       <c r="L103" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M103" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -5616,50 +5494,32 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K104" s="3" t="n">
         <v>0</v>
@@ -5667,10 +5527,8 @@
       <c r="L104" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M104" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -5679,50 +5537,32 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K105" s="3" t="n">
         <v>0</v>
@@ -5730,10 +5570,8 @@
       <c r="L105" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -5742,61 +5580,41 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="F106" s="3" t="n">
+        <v>-0.012</v>
+      </c>
+      <c r="G106" s="3" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="H106" s="3" t="n">
+        <v>-0.592</v>
+      </c>
+      <c r="I106" s="3" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="J106" s="3" t="n">
+        <v>-0.713</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0</v>
+        <v>-0.045</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.016</v>
+      </c>
+      <c r="M106" s="3" t="n">
+        <v>0.045</v>
       </c>
     </row>
     <row r="107">
@@ -5805,50 +5623,32 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>0.646</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>0.836</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="F107" s="3" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="G107" s="3" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="H107" s="3" t="n">
+        <v>0.478</v>
+      </c>
+      <c r="I107" s="3" t="n">
+        <v>0.196</v>
+      </c>
+      <c r="J107" s="3" t="n">
+        <v>1.093</v>
       </c>
       <c r="K107" s="3" t="n">
         <v>1.441</v>
@@ -5856,10 +5656,8 @@
       <c r="L107" s="3" t="n">
         <v>3.027</v>
       </c>
-      <c r="M107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M107" s="3" t="n">
+        <v>2.588</v>
       </c>
     </row>
     <row r="108">
@@ -5868,50 +5666,32 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K108" s="3" t="n">
         <v>0</v>
@@ -5919,10 +5699,8 @@
       <c r="L108" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -5931,50 +5709,32 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K109" s="3" t="n">
         <v>0</v>
@@ -5982,10 +5742,8 @@
       <c r="L109" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -5994,50 +5752,32 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K110" s="3" t="n">
         <v>0</v>
@@ -6045,10 +5785,8 @@
       <c r="L110" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -6057,50 +5795,32 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K111" s="3" t="n">
         <v>0</v>
@@ -6108,10 +5828,8 @@
       <c r="L111" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -6120,50 +5838,32 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K112" s="3" t="n">
         <v>0</v>
@@ -6171,10 +5871,8 @@
       <c r="L112" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -6183,50 +5881,32 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K113" s="3" t="n">
         <v>0</v>
@@ -6234,10 +5914,8 @@
       <c r="L113" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -6246,50 +5924,32 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K114" s="3" t="n">
         <v>0</v>
@@ -6297,10 +5957,8 @@
       <c r="L114" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -6309,50 +5967,32 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K115" s="3" t="n">
         <v>0</v>
@@ -6360,10 +6000,8 @@
       <c r="L115" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -6372,50 +6010,32 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K116" s="3" t="n">
         <v>0</v>
@@ -6423,10 +6043,8 @@
       <c r="L116" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -6435,50 +6053,32 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K117" s="3" t="n">
         <v>0</v>
@@ -6486,10 +6086,8 @@
       <c r="L117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -6498,50 +6096,32 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K118" s="3" t="n">
         <v>0</v>
@@ -6549,10 +6129,8 @@
       <c r="L118" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -6596,15 +6174,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I119" s="3" t="n">
+        <v>-3.356</v>
+      </c>
+      <c r="J119" s="3" t="n">
+        <v>-39.889</v>
       </c>
       <c r="K119" s="3" t="n">
         <v>-5.001</v>
@@ -6612,10 +6186,8 @@
       <c r="L119" s="3" t="n">
         <v>-7.217</v>
       </c>
-      <c r="M119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M119" s="3" t="n">
+        <v>-3.946</v>
       </c>
     </row>
     <row r="120">
@@ -6624,50 +6196,32 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K120" s="3" t="n">
         <v>0</v>
@@ -6675,10 +6229,8 @@
       <c r="L120" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -6687,50 +6239,32 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K121" s="3" t="n">
         <v>0</v>
@@ -6738,10 +6272,8 @@
       <c r="L121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -6750,50 +6282,32 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K122" s="3" t="n">
         <v>0</v>
@@ -6801,10 +6315,8 @@
       <c r="L122" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -6813,50 +6325,32 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K123" s="3" t="n">
         <v>0</v>
@@ -6864,10 +6358,8 @@
       <c r="L123" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -6876,50 +6368,32 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K124" s="3" t="n">
         <v>0</v>
@@ -6927,10 +6401,8 @@
       <c r="L124" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -6939,50 +6411,32 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K125" s="3" t="n">
         <v>0</v>
@@ -6990,10 +6444,8 @@
       <c r="L125" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -7002,50 +6454,32 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K126" s="3" t="n">
         <v>0</v>
@@ -7053,10 +6487,8 @@
       <c r="L126" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -7132,50 +6564,32 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" s="3" t="n">
+        <v>-0.177</v>
+      </c>
+      <c r="H128" s="3" t="n">
+        <v>-0.322</v>
+      </c>
+      <c r="I128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" s="3" t="n">
+        <v>-1.104</v>
       </c>
       <c r="K128" s="3" t="n">
         <v>0</v>
@@ -7183,10 +6597,8 @@
       <c r="L128" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -7230,15 +6642,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I129" s="3" t="n">
+        <v>-0.057</v>
+      </c>
+      <c r="J129" s="3" t="n">
+        <v>44.092</v>
       </c>
       <c r="K129" s="3" t="n">
         <v>0.287</v>
@@ -7246,10 +6654,8 @@
       <c r="L129" s="3" t="n">
         <v>6.216</v>
       </c>
-      <c r="M129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M129" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -7258,50 +6664,32 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>0.001014</v>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="D130" s="3" t="n">
+        <v>27.614</v>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>9.545</v>
+      </c>
+      <c r="F130" s="3" t="n">
+        <v>3.581</v>
+      </c>
+      <c r="G130" s="3" t="n">
+        <v>1.605</v>
+      </c>
+      <c r="H130" s="3" t="n">
+        <v>7.004</v>
+      </c>
+      <c r="I130" s="3" t="n">
+        <v>10.179</v>
+      </c>
+      <c r="J130" s="3" t="n">
+        <v>3.132</v>
       </c>
       <c r="K130" s="3" t="n">
         <v>19.643</v>
@@ -7309,10 +6697,8 @@
       <c r="L130" s="3" t="n">
         <v>10.852</v>
       </c>
-      <c r="M130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M130" s="3" t="n">
+        <v>6.794</v>
       </c>
     </row>
     <row r="131">
@@ -7321,50 +6707,32 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K131" s="3" t="n">
         <v>0</v>
@@ -7372,10 +6740,8 @@
       <c r="L131" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -7384,50 +6750,32 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>0.414848</v>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>27.198</v>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>-18.069</v>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>-5.964</v>
+      </c>
+      <c r="F132" s="3" t="n">
+        <v>-1.976</v>
+      </c>
+      <c r="G132" s="3" t="n">
+        <v>5.399</v>
+      </c>
+      <c r="H132" s="3" t="n">
+        <v>3.175</v>
+      </c>
+      <c r="I132" s="3" t="n">
+        <v>-7.047</v>
+      </c>
+      <c r="J132" s="3" t="n">
+        <v>-0.123</v>
       </c>
       <c r="K132" s="3" t="n">
         <v>-8.791</v>
@@ -7435,10 +6783,8 @@
       <c r="L132" s="3" t="n">
         <v>-4.058</v>
       </c>
-      <c r="M132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M132" s="3" t="n">
+        <v>-5.086</v>
       </c>
     </row>
     <row r="133">
@@ -7447,50 +6793,32 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>0.415862</v>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>27.614</v>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>9.545</v>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>3.581</v>
+      </c>
+      <c r="F133" s="3" t="n">
+        <v>1.605</v>
+      </c>
+      <c r="G133" s="3" t="n">
+        <v>7.004</v>
+      </c>
+      <c r="H133" s="3" t="n">
+        <v>10.179</v>
+      </c>
+      <c r="I133" s="3" t="n">
+        <v>3.132</v>
+      </c>
+      <c r="J133" s="3" t="n">
+        <v>3.009</v>
       </c>
       <c r="K133" s="3" t="n">
         <v>10.852</v>
@@ -7498,10 +6826,8 @@
       <c r="L133" s="3" t="n">
         <v>6.794</v>
       </c>
-      <c r="M133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M133" s="3" t="n">
+        <v>1.708</v>
       </c>
     </row>
     <row r="134">
@@ -7510,50 +6836,32 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K134" s="3" t="n">
         <v>0</v>
@@ -7561,10 +6869,8 @@
       <c r="L134" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -7608,15 +6914,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I135" s="3" t="n">
+        <v>-4.029</v>
+      </c>
+      <c r="J135" s="3" t="n">
+        <v>-4.288</v>
       </c>
       <c r="K135" s="3" t="n">
         <v>-4.038</v>
@@ -7624,10 +6926,8 @@
       <c r="L135" s="3" t="n">
         <v>-3.022</v>
       </c>
-      <c r="M135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M135" s="3" t="n">
+        <v>-2.133</v>
       </c>
     </row>
   </sheetData>
@@ -7641,7 +6941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P201"/>
+  <dimension ref="A1:P278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11292,7 +10592,11 @@
           <t>Lease obligations</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -20467,7 +19771,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Net (loss)/income for the year $</t>
+          <t>Net loss for the year $</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -20495,41 +19799,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N176" s="5" t="n">
-        <v>21.564</v>
+      <c r="I176" s="5" t="n">
+        <v>-92.348</v>
+      </c>
+      <c r="J176" s="5" t="n">
+        <v>-3.196</v>
+      </c>
+      <c r="K176" s="5" t="n">
+        <v>-4.198</v>
+      </c>
+      <c r="L176" s="5" t="n">
+        <v>-4.744</v>
+      </c>
+      <c r="M176" s="5" t="n">
+        <v>-13.085</v>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O176" s="5" t="n">
         <v>-20.772</v>
       </c>
-      <c r="P176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P176" s="5" t="n">
+        <v>-119.776</v>
       </c>
     </row>
     <row r="177">
@@ -20604,10 +19898,8 @@
       <c r="O177" s="5" t="n">
         <v>3.027</v>
       </c>
-      <c r="P177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P177" s="5" t="n">
+        <v>2.588</v>
       </c>
     </row>
     <row r="178">
@@ -20682,10 +19974,8 @@
       <c r="O178" s="5" t="n">
         <v>0.014</v>
       </c>
-      <c r="P178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P178" s="5" t="n">
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="179">
@@ -20701,7 +19991,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Interest on lease obligations</t>
+          <t>Share of loss from investment in associates 4</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
@@ -20751,17 +20041,13 @@
         </is>
       </c>
       <c r="N179" s="5" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="O179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.025</v>
+      </c>
+      <c r="O179" s="5" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="P179" s="5" t="n">
+        <v>0.02</v>
       </c>
     </row>
     <row r="180">
@@ -20777,7 +20063,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Share of loss from investment in associates 4</t>
+          <t>Unrealized foreign exchange loss</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
@@ -20827,15 +20113,13 @@
         </is>
       </c>
       <c r="N180" s="5" t="n">
-        <v>0.025</v>
+        <v>0.041</v>
       </c>
       <c r="O180" s="5" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="P180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.033</v>
+      </c>
+      <c r="P180" s="5" t="n">
+        <v>0.007</v>
       </c>
     </row>
     <row r="181">
@@ -20851,7 +20135,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Unrealized foreign exchange loss</t>
+          <t>Impairment of intangible exploration assets 5</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
@@ -20900,11 +20184,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N181" s="5" t="n">
-        <v>0.041</v>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O181" s="5" t="n">
-        <v>0.033</v>
+        <v>14.676</v>
       </c>
       <c r="P181" t="inlineStr">
         <is>
@@ -20925,7 +20211,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Impairment of intangible exploration assets 5</t>
+          <t>Loss on revaluation of financial asset 4</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
@@ -20979,13 +20265,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O182" s="5" t="n">
-        <v>14.676</v>
-      </c>
-      <c r="P182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P182" s="5" t="n">
+        <v>114.158</v>
       </c>
     </row>
     <row r="183">
@@ -21001,7 +20287,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Gain on revaluation of financial asset 4</t>
+          <t>Non-cash finance expense</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
@@ -21050,18 +20336,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N183" s="5" t="n">
-        <v>-27.098</v>
-      </c>
-      <c r="O183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O183" s="5" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="P183" s="5" t="n">
+        <v>0.014</v>
       </c>
     </row>
     <row r="184">
@@ -21077,10 +20361,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Changes in non-cash operating working capital 17</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr"/>
+          <t>Changes in non-cash operating working capital 18</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
           <t>-</t>
@@ -21126,16 +20414,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N184" s="5" t="n">
-        <v>-0.045</v>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O184" s="5" t="n">
         <v>-0.016</v>
       </c>
-      <c r="P184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P184" s="5" t="n">
+        <v>0.045</v>
       </c>
     </row>
     <row r="185">
@@ -21210,10 +20498,8 @@
       <c r="O185" s="5" t="n">
         <v>-3.022</v>
       </c>
-      <c r="P185" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P185" s="5" t="n">
+        <v>-2.133</v>
       </c>
     </row>
     <row r="186">
@@ -21319,20 +20605,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G187" s="5" t="n">
+        <v>-34.261</v>
+      </c>
+      <c r="H187" s="5" t="n">
+        <v>-2.066</v>
+      </c>
+      <c r="I187" s="5" t="n">
+        <v>-1.202</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
@@ -21508,10 +20788,8 @@
       <c r="O189" s="5" t="n">
         <v>-0.469</v>
       </c>
-      <c r="P189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P189" s="5" t="n">
+        <v>-1.017</v>
       </c>
     </row>
     <row r="190">
@@ -21527,7 +20805,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Changes in non-cash investing working capital 17</t>
+          <t>Changes in non-cash investing working capital 18</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
@@ -21576,16 +20854,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N190" s="5" t="n">
-        <v>-0.008999999999999999</v>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O190" s="5" t="n">
         <v>1.405</v>
       </c>
-      <c r="P190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P190" s="5" t="n">
+        <v>-2.929</v>
       </c>
     </row>
     <row r="191">
@@ -21644,15 +20922,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L191" s="5" t="n">
+        <v>-3.356</v>
+      </c>
+      <c r="M191" s="5" t="n">
+        <v>-39.889</v>
       </c>
       <c r="N191" s="5" t="n">
         <v>-5.001</v>
@@ -21660,10 +20934,8 @@
       <c r="O191" s="5" t="n">
         <v>-7.217</v>
       </c>
-      <c r="P191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P191" s="5" t="n">
+        <v>-3.946</v>
       </c>
     </row>
     <row r="192">
@@ -21753,7 +21025,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Promissory notes 11</t>
+          <t>Promissory notes 14</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
@@ -21810,10 +21082,8 @@
       <c r="O193" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="P193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P193" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="194">
@@ -21829,10 +21099,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Payment of lease obligations</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr"/>
+          <t>Net cash provided by financing activities</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
@@ -21879,17 +21153,13 @@
         </is>
       </c>
       <c r="N194" s="5" t="n">
-        <v>-0.033</v>
-      </c>
-      <c r="O194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.287</v>
+      </c>
+      <c r="O194" s="5" t="n">
+        <v>6.216</v>
+      </c>
+      <c r="P194" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="195">
@@ -21900,74 +21170,52 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Financing</t>
+          <t>Effect of exchange rate changes on cash and</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Effect of exchange rate changes on cash and cash equivalents denominated in foreign currency</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F195" s="5" t="n">
+        <v>-0.467</v>
+      </c>
+      <c r="G195" s="5" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="H195" s="5" t="n">
+        <v>-0.048</v>
+      </c>
+      <c r="I195" s="5" t="n">
+        <v>-0.019</v>
+      </c>
+      <c r="J195" s="5" t="n">
+        <v>-0.151</v>
+      </c>
+      <c r="K195" s="5" t="n">
+        <v>0.163</v>
+      </c>
+      <c r="L195" s="5" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="M195" s="5" t="n">
+        <v>-0.038</v>
       </c>
       <c r="N195" s="5" t="n">
-        <v>0.287</v>
+        <v>-0.039</v>
       </c>
       <c r="O195" s="5" t="n">
-        <v>6.216</v>
-      </c>
-      <c r="P195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.035</v>
+      </c>
+      <c r="P195" s="5" t="n">
+        <v>-0.007</v>
       </c>
     </row>
     <row r="196">
@@ -21983,10 +21231,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Effect of exchange rate changes on cash and cash equivalents denominated in foreign currency</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr"/>
+          <t>Decrease in cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
           <t>-</t>
@@ -21997,20 +21249,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G196" s="5" t="n">
+        <v>-18.069</v>
+      </c>
+      <c r="H196" s="5" t="n">
+        <v>-5.964</v>
+      </c>
+      <c r="I196" s="5" t="n">
+        <v>-1.976</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
@@ -22022,26 +21268,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L196" s="5" t="n">
+        <v>-7.047</v>
+      </c>
+      <c r="M196" s="5" t="n">
+        <v>-0.123</v>
       </c>
       <c r="N196" s="5" t="n">
-        <v>-0.039</v>
+        <v>-8.791</v>
       </c>
       <c r="O196" s="5" t="n">
-        <v>-0.035</v>
-      </c>
-      <c r="P196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4.058</v>
+      </c>
+      <c r="P196" s="5" t="n">
+        <v>-5.086</v>
       </c>
     </row>
     <row r="197">
@@ -22057,12 +21297,12 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Decrease in cash and cash equivalents</t>
+          <t>Cash and cash equivalents, beginning of the year $</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -22070,56 +21310,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F197" s="5" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="G197" s="5" t="n">
+        <v>27.614</v>
+      </c>
+      <c r="H197" s="5" t="n">
+        <v>9.545</v>
+      </c>
+      <c r="I197" s="5" t="n">
+        <v>3.581</v>
+      </c>
+      <c r="J197" s="5" t="n">
+        <v>1.605</v>
+      </c>
+      <c r="K197" s="5" t="n">
+        <v>7.004</v>
+      </c>
+      <c r="L197" s="5" t="n">
+        <v>10.179</v>
+      </c>
+      <c r="M197" s="5" t="n">
+        <v>3.132</v>
       </c>
       <c r="N197" s="5" t="n">
-        <v>-8.791</v>
+        <v>19.643</v>
       </c>
       <c r="O197" s="5" t="n">
-        <v>-4.058</v>
-      </c>
-      <c r="P197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>10.852</v>
+      </c>
+      <c r="P197" s="5" t="n">
+        <v>6.794</v>
       </c>
     </row>
     <row r="198">
@@ -22135,12 +21357,12 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, beginning of the year $</t>
+          <t>Cash and cash equivalents, end of the year $</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -22148,56 +21370,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F198" s="5" t="n">
+        <v>27.614</v>
+      </c>
+      <c r="G198" s="5" t="n">
+        <v>9.545</v>
+      </c>
+      <c r="H198" s="5" t="n">
+        <v>3.581</v>
+      </c>
+      <c r="I198" s="5" t="n">
+        <v>1.605</v>
+      </c>
+      <c r="J198" s="5" t="n">
+        <v>7.004</v>
+      </c>
+      <c r="K198" s="5" t="n">
+        <v>10.179</v>
+      </c>
+      <c r="L198" s="5" t="n">
+        <v>3.132</v>
+      </c>
+      <c r="M198" s="5" t="n">
+        <v>3.009</v>
       </c>
       <c r="N198" s="5" t="n">
-        <v>19.643</v>
+        <v>10.852</v>
       </c>
       <c r="O198" s="5" t="n">
-        <v>10.852</v>
-      </c>
-      <c r="P198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.794</v>
+      </c>
+      <c r="P198" s="5" t="n">
+        <v>1.708</v>
       </c>
     </row>
     <row r="199">
@@ -22208,17 +21412,17 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Effect of exchange rate changes on cash and</t>
+          <t>Supplementary information</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, end of the year $</t>
+          <t>Interest paid</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>InterestPaidSupplementalData</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -22266,11 +21470,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N199" s="5" t="n">
-        <v>10.852</v>
-      </c>
-      <c r="O199" s="5" t="n">
-        <v>6.794</v>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P199" t="inlineStr">
         <is>
@@ -22291,14 +21499,10 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Interest paid</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>InterestPaidSupplementalData</t>
-        </is>
-      </c>
+          <t>Taxes paid</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -22368,15 +21572,19 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Supplementary information</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Taxes paid</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr"/>
+          <t>Net (loss)/income for the year $</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
@@ -22422,17 +21630,5775 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N201" s="5" t="n">
+        <v>21.564</v>
+      </c>
+      <c r="O201" s="5" t="n">
+        <v>-20.772</v>
       </c>
       <c r="P201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Interest on lease obligations</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N202" s="5" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Gain on revaluation of financial asset 4</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N203" s="5" t="n">
+        <v>-27.098</v>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Changes in non-cash operating working capital 17</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N204" s="5" t="n">
+        <v>-0.045</v>
+      </c>
+      <c r="O204" s="5" t="n">
+        <v>-0.016</v>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Investing</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Changes in non-cash investing working capital 17</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N205" s="5" t="n">
+        <v>-0.008999999999999999</v>
+      </c>
+      <c r="O205" s="5" t="n">
+        <v>1.405</v>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Financing</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Promissory notes 11</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O206" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Financing</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Payment of lease obligations</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N207" s="5" t="n">
+        <v>-0.033</v>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Item not affecting cash</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Stock-based compensation 9</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F208" s="5" t="n">
+        <v>0.646</v>
+      </c>
+      <c r="G208" s="5" t="n">
+        <v>0.836</v>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L208" s="5" t="n">
+        <v>0.196</v>
+      </c>
+      <c r="M208" s="5" t="n">
+        <v>1.093</v>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Item not affecting cash</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Depreciation 6</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L209" s="5" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="M209" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Item not affecting cash</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Gain on disposal of property and equipment 6</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M210" s="5" t="n">
+        <v>-0.023</v>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Item not affecting cash</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Share of loss from equity investments 5</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L211" s="5" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="M211" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Item not affecting cash</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Unrealized foreign exchange (gain)/loss</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J212" s="5" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="K212" s="5" t="n">
+        <v>-0.163</v>
+      </c>
+      <c r="L212" s="5" t="n">
+        <v>-0.395</v>
+      </c>
+      <c r="M212" s="5" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Item not affecting cash</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Writedown of investment 5</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M213" s="5" t="n">
+        <v>8.202</v>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Item not affecting cash</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Changes in non-cash operating working capital 19</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L214" s="5" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="M214" s="5" t="n">
+        <v>-0.713</v>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Item not affecting cash</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Net cash used in operating activities</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L215" s="5" t="n">
+        <v>-4.029</v>
+      </c>
+      <c r="M215" s="5" t="n">
+        <v>-4.288</v>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Investing</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Property and equipment expenditures 6</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L216" s="5" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="M216" s="5" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Investing</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Proceeds from disposition of property and equipment 6</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M217" s="5" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Investing</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Intangible exploration expenditures 7</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L218" s="5" t="n">
+        <v>-0.157</v>
+      </c>
+      <c r="M218" s="5" t="n">
+        <v>-0.142</v>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Investing</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Investment in associates 5</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L219" s="5" t="n">
+        <v>-7.278</v>
+      </c>
+      <c r="M219" s="5" t="n">
+        <v>-35.298</v>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Investing</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Changes in non-cash investing working capital 19</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L220" s="5" t="n">
+        <v>4.083</v>
+      </c>
+      <c r="M220" s="5" t="n">
+        <v>-4.479</v>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Financing</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Common shares issued 8(b)</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M221" s="5" t="n">
+        <v>45.196</v>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Financing</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Share issuance costs 8(b)</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M222" s="5" t="n">
+        <v>-1.104</v>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Financing</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Advances from related party 13</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G223" s="5" t="n">
+        <v>1.491</v>
+      </c>
+      <c r="H223" s="5" t="n">
+        <v>1.037</v>
+      </c>
+      <c r="I223" s="5" t="n">
+        <v>1.017</v>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L223" s="5" t="n">
+        <v>0.243</v>
+      </c>
+      <c r="M223" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Financing</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Payments to related party 13</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G224" s="5" t="n">
+        <v>-1.918</v>
+      </c>
+      <c r="H224" s="5" t="n">
+        <v>-0.922</v>
+      </c>
+      <c r="I224" s="5" t="n">
+        <v>-1.037</v>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L224" s="5" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="M224" s="5" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Financing</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Net cash provided by/(used in) financing activities</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L225" s="5" t="n">
+        <v>-0.057</v>
+      </c>
+      <c r="M225" s="5" t="n">
+        <v>44.092</v>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Item not affecting cash</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Stock-based compensation 10</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J226" s="5" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="K226" s="5" t="n">
+        <v>0.478</v>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Item not affecting cash</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Depreciation 7</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J227" s="5" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="K227" s="5" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Item not affecting cash</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Changes in non-cash operating w orking capital 20</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J228" s="5" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="K228" s="5" t="n">
+        <v>-0.592</v>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Item not affecting cash</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Item not affecting cash total</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" s="5" t="n">
+        <v>-0.067493</v>
+      </c>
+      <c r="F229" s="5" t="n">
+        <v>-1.893</v>
+      </c>
+      <c r="G229" s="5" t="n">
+        <v>-1.384</v>
+      </c>
+      <c r="H229" s="5" t="n">
+        <v>-1.384</v>
+      </c>
+      <c r="I229" s="5" t="n">
+        <v>-1.445</v>
+      </c>
+      <c r="J229" s="5" t="n">
+        <v>-2.273</v>
+      </c>
+      <c r="K229" s="5" t="n">
+        <v>-4.41</v>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Investing</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Property and equipment expenditures 7</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr"/>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J230" s="5" t="n">
+        <v>-0.129</v>
+      </c>
+      <c r="K230" s="5" t="n">
+        <v>-0.063</v>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Investing</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Intangible exploration expenditures 8</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr"/>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K231" s="5" t="n">
+        <v>-0.424</v>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Investing</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Acquisition of Block 2B 5, 6(i)</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K232" s="5" t="n">
+        <v>-3.232</v>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Investing</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Changes in non-cash investing w orking capital 20</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J233" s="5" t="n">
+        <v>-0.231</v>
+      </c>
+      <c r="K233" s="5" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Investing</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Investing total</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
+      <c r="E234" s="5" t="n">
+        <v>-1.266631</v>
+      </c>
+      <c r="F234" s="5" t="n">
+        <v>29.554</v>
+      </c>
+      <c r="G234" s="5" t="n">
+        <v>-34.999</v>
+      </c>
+      <c r="H234" s="5" t="n">
+        <v>-4.647</v>
+      </c>
+      <c r="I234" s="5" t="n">
+        <v>-0.492</v>
+      </c>
+      <c r="J234" s="5" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="K234" s="5" t="n">
+        <v>-3.388</v>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Financing</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Common shares issued 9(b)</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J235" s="5" t="n">
+        <v>8.368</v>
+      </c>
+      <c r="K235" s="5" t="n">
+        <v>11.162</v>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Financing</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Share issuance costs 9(b)</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J236" s="5" t="n">
+        <v>-0.177</v>
+      </c>
+      <c r="K236" s="5" t="n">
+        <v>-0.322</v>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Financing</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Advances from related party 14</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J237" s="5" t="n">
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="K237" s="5" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Financing</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Payments to related party 14</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J238" s="5" t="n">
+        <v>-0.572</v>
+      </c>
+      <c r="K238" s="5" t="n">
+        <v>-0.264</v>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Financing</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Financing total</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
+      <c r="E239" s="5" t="n">
+        <v>1.748972</v>
+      </c>
+      <c r="F239" s="5" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="G239" s="5" t="n">
+        <v>18.009</v>
+      </c>
+      <c r="H239" s="5" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="I239" s="5" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="J239" s="5" t="n">
+        <v>8.183</v>
+      </c>
+      <c r="K239" s="5" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Effect of exchange rate changes on cash and</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Increase in cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E240" s="5" t="n">
+        <v>0.414848</v>
+      </c>
+      <c r="F240" s="5" t="n">
+        <v>27.197639</v>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J240" s="5" t="n">
+        <v>5.399</v>
+      </c>
+      <c r="K240" s="5" t="n">
+        <v>3.175</v>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Item not affecting cash</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Stock-based compensation 8</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G241" s="5" t="n">
+        <v>0.836</v>
+      </c>
+      <c r="H241" s="5" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="I241" s="5" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="J241" s="5" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Item not affecting cash</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Depreciation 5</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J242" s="5" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Item not affecting cash</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Fair market value adjustment - w arrants</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I243" s="5" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Item not affecting cash</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Unrealized foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr"/>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F244" s="5" t="n">
+        <v>0.466638</v>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H244" s="5" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="I244" s="5" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="J244" s="5" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Item not affecting cash</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Impairment of intangible exploration assets</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr"/>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I245" s="5" t="n">
+        <v>90.56999999999999</v>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Item not affecting cash</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Changes in non-cash operating w orking capital 19</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I246" s="5" t="n">
+        <v>-0.012</v>
+      </c>
+      <c r="J246" s="5" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Investing</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Property and equipment expenditures 5</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr"/>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J247" s="5" t="n">
+        <v>-0.129</v>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Investing</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Intangible exploration expenditures 6</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr"/>
+      <c r="E248" s="5" t="n">
+        <v>-0.924722</v>
+      </c>
+      <c r="F248" s="5" t="n">
+        <v>-14.198</v>
+      </c>
+      <c r="G248" s="5" t="n">
+        <v>-34.261</v>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I248" s="5" t="n">
+        <v>-1.202</v>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Investing</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Changes in non-cash investing w orking capital 19</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr"/>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I249" s="5" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="J249" s="5" t="n">
+        <v>-0.231</v>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Financing</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Common shares issued, net of issuance costs 7(b)</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr"/>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J250" s="5" t="n">
+        <v>8.191000000000001</v>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Financing</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Advances from related party 12</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr"/>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I251" s="5" t="n">
+        <v>1.017</v>
+      </c>
+      <c r="J251" s="5" t="n">
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Financing</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Payments to related party 12</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I252" s="5" t="n">
+        <v>-1.037</v>
+      </c>
+      <c r="J252" s="5" t="n">
+        <v>-0.572</v>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Effect of exchange rate changes on cash and</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Increase (decrease) in cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F253" s="5" t="n">
+        <v>27.198</v>
+      </c>
+      <c r="G253" s="5" t="n">
+        <v>-18.069</v>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I253" s="5" t="n">
+        <v>-1.976</v>
+      </c>
+      <c r="J253" s="5" t="n">
+        <v>5.399</v>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Net income (loss) for the year $</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F254" s="5" t="n">
+        <v>-1.098</v>
+      </c>
+      <c r="G254" s="5" t="n">
+        <v>2.979</v>
+      </c>
+      <c r="H254" s="5" t="n">
+        <v>2.205</v>
+      </c>
+      <c r="I254" s="5" t="n">
+        <v>-92.348</v>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Item not affecting cash</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Impairment of intangible exploration assets 5</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr"/>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I255" s="5" t="n">
+        <v>90.56999999999999</v>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Item not affecting cash</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Fair market value adjustment - w arrants 7</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr"/>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G256" s="5" t="n">
+        <v>-4.874</v>
+      </c>
+      <c r="H256" s="5" t="n">
+        <v>-4.135</v>
+      </c>
+      <c r="I256" s="5" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Item not affecting cash</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Changes in non-cash operating w orking capital 18</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G257" s="5" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="H257" s="5" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="I257" s="5" t="n">
+        <v>-0.012</v>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Investing</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Changes in non-cash investing w orking capital 18</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr"/>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G258" s="5" t="n">
+        <v>-0.738</v>
+      </c>
+      <c r="H258" s="5" t="n">
+        <v>-2.581</v>
+      </c>
+      <c r="I258" s="5" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Net income for the year $</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G259" s="5" t="n">
+        <v>2.979</v>
+      </c>
+      <c r="H259" s="5" t="n">
+        <v>2.205</v>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Item not affecting cash</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Unrealized foreign exchange (gain) loss</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr"/>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F260" s="5" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="G260" s="5" t="n">
+        <v>-0.305</v>
+      </c>
+      <c r="H260" s="5" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Financing</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Common shares and w arrants issued, net of issuance costs 6(b),7</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr"/>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G261" s="5" t="n">
+        <v>16.948</v>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Financing</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Repayment of an advance issued to a related party 13</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr"/>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G262" s="5" t="n">
+        <v>1.488</v>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Item not affecting cash</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Loss on reverse acquisition 5</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr"/>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F263" s="5" t="n">
+        <v>4.579</v>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Item not affecting cash</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Fair market value adjustment - warrants 8</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr"/>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F264" s="5" t="n">
+        <v>-6.488</v>
+      </c>
+      <c r="G264" s="5" t="n">
+        <v>-4.874</v>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Item not affecting cash</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Changes in non-cash operating working capital</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F265" s="5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G265" s="5" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Investing</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Cash received on business acquisitions 5</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr"/>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F266" s="5" t="n">
+        <v>40.506</v>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Investing</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Changes in non-cash investing working capital</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr"/>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F267" s="5" t="n">
+        <v>3.246</v>
+      </c>
+      <c r="G267" s="5" t="n">
+        <v>-0.738</v>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Financing</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Common shares and warrants issued, net of issuance costs 7(b),8</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr"/>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G268" s="5" t="n">
+        <v>16.948</v>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Financing</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Advances from related party 15</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr"/>
+      <c r="E269" s="5" t="n">
+        <v>1.748972</v>
+      </c>
+      <c r="F269" s="5" t="n">
+        <v>8.846</v>
+      </c>
+      <c r="G269" s="5" t="n">
+        <v>1.491</v>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Financing</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Payments to related party 15</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr"/>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F270" s="5" t="n">
+        <v>-8.842000000000001</v>
+      </c>
+      <c r="G270" s="5" t="n">
+        <v>-1.918</v>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Financing</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Repayment of an advance issued to a related party 15</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr"/>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G271" s="5" t="n">
+        <v>1.488</v>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Net loss for the period $</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E272" s="5" t="n">
+        <v>-0.067493</v>
+      </c>
+      <c r="F272" s="5" t="n">
+        <v>-1.098903</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Item not affecting cash</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Fair market value adjustment - w arrants 8</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr"/>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F273" s="5" t="n">
+        <v>-6.488154</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Item not affecting cash</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Changes in non-cash operating w orking capital</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F274" s="5" t="n">
+        <v>0.001102</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Investing</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Changes in non-cash investing w orking capital</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr"/>
+      <c r="E275" s="5" t="n">
+        <v>-0.341909</v>
+      </c>
+      <c r="F275" s="5" t="n">
+        <v>3.245946</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Financing</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Repayments to related party 15</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr"/>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F276" s="5" t="n">
+        <v>-8.841571999999999</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Effect of exchange rate changes on cash and</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents, beginning of year $</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E277" s="5" t="n">
+        <v>0.001014</v>
+      </c>
+      <c r="F277" s="5" t="n">
+        <v>0.415862</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Effect of exchange rate changes on cash and</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents, end of year $</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E278" s="5" t="n">
+        <v>0.415862</v>
+      </c>
+      <c r="F278" s="5" t="n">
+        <v>27.613501</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P278" t="inlineStr">
         <is>
           <t>-</t>
         </is>
